--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91953</v>
+        <v>91960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>91971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91972</v>
+        <v>91975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91975</v>
+        <v>91977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91982</v>
+        <v>91985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>92013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>92013</v>
+        <v>92019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129296100</v>
       </c>
       <c r="B3" t="n">
-        <v>92019</v>
+        <v>92020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129296086</v>
+        <v>129296100</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -765,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Lundqvist</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129296100</v>
+        <v>129296086</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Andreas Lundqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 38991-2022 artfynd.xlsx
+++ b/artfynd/A 38991-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296086</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>